--- a/CardData/ActionCard.xlsx
+++ b/CardData/ActionCard.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>1792414518127612</author>
+    <author>1792479860715753</author>
   </authors>
   <commentList>
     <comment ref="E3" authorId="0">
@@ -67,19 +67,19 @@
     <t>string</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(array#sep=_),int</t>
+    <t xml:space="preserve">(array#sep=,), (array#sep=_),int</t>
   </si>
   <si>
     <t>string</t>
@@ -239,7 +239,7 @@
 若处于【连击】状态，敌方生命值再-1。</t>
   </si>
   <si>
-    <t>10_1_0,3_-1_1</t>
+    <t>10_0_0,3_-1_1</t>
   </si>
   <si>
     <t>c_0</t>
@@ -253,7 +253,7 @@
 若处于【连击】状态，敌方生命值再-1。</t>
   </si>
   <si>
-    <t>10_1_0,3_-2_1</t>
+    <t>10_0_0,3_-2_1</t>
   </si>
   <si>
     <t>c_0</t>
@@ -263,9 +263,6 @@
   </si>
   <si>
     <t>不可使用，只能用于蓄能。</t>
-  </si>
-  <si>
-    <t>null</t>
   </si>
   <si>
     <t>null</t>
@@ -290,7 +287,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -308,11 +305,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="BlinkMacSystemFont"/>
-      <color rgb="000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -358,7 +350,7 @@
     <xf numFmtId="164" fontId="3" fillId="2" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf fontId="4" fillId="2" applyFont="1" applyFill="1">
+    <xf numFmtId="164" fontId="2" fillId="2" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="3" applyFont="1">
@@ -367,13 +359,13 @@
     <xf numFmtId="164" fontId="3" applyNumberFormat="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf fontId="5" applyFont="1">
+    <xf fontId="4" applyFont="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="164" fontId="5" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -752,7 +744,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>57</v>
@@ -842,7 +834,7 @@
         <v>3</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>69</v>
@@ -885,11 +877,11 @@
       <c r="F16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -897,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>0</v>
@@ -909,13 +901,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="18">
